--- a/examples/fao_a3/excel/informe.xlsx
+++ b/examples/fao_a3/excel/informe.xlsx
@@ -6473,7 +6473,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ROB portones [kgf]</t>
+          <t>ROB par de portones [kgf]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
         <v>1.356990427108308</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.69858020902099</v>
+        <v>35.39716041804198</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>426.1672050628522</v>
@@ -6579,7 +6579,7 @@
         <v>3.053228460993694</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>39.82180547029723</v>
+        <v>79.64361094059446</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>640.0885124665494</v>
@@ -6608,7 +6608,7 @@
         <v>5.427961708433234</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70.79432083608397</v>
+        <v>141.5886416721679</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>930.1169194410903</v>
@@ -6637,7 +6637,7 @@
         <v>8.481190169426929</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>110.6161263063812</v>
+        <v>221.2322526127624</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1290.103043217242</v>
@@ -6666,7 +6666,7 @@
         <v>12.21291384397478</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>159.2872218811889</v>
+        <v>318.5744437623778</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1715.964419341012</v>
@@ -6695,7 +6695,7 @@
         <v>16.62313273207678</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>216.8076075605071</v>
+        <v>433.6152151210143</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>2200.483713451298</v>
@@ -6724,7 +6724,7 @@
         <v>21.71184683373293</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>283.1772833443359</v>
+        <v>566.3545666886718</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>2740.224960203204</v>
@@ -6753,7 +6753,7 @@
         <v>27.47905614894325</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>358.3962492326751</v>
+        <v>716.7924984653503</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>3331.215009213285</v>
@@ -6782,7 +6782,7 @@
         <v>33.92476067770772</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>442.4645052255249</v>
+        <v>884.9290104510497</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3969.866441169024</v>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 2 kn</t>
+          <t>ROB hidrodinámica de un portón a 2 kn</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 3 kn</t>
+          <t>ROB hidrodinámica de un portón a 3 kn</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 3.5 kn</t>
+          <t>ROB hidrodinámica de un portón a 3.5 kn</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">

--- a/examples/fao_a3/excel/informe.xlsx
+++ b/examples/fao_a3/excel/informe.xlsx
@@ -1921,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -2294,7 +2294,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>warp_undersized</t>
+          <t>warp_cd_horizontal_angle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E267:E272</t>
+          <t>E103:E106</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cable de 12 mm (8.55 t) seleccionado con carga mínima requerida de 8.8 t.</t>
+          <t>El CD del cable se toma con la divergencia en planta δ2 = 4.3° (→ 0.02) en vez del ángulo de ataque del cable al flujo, y por la fila más cercana de la tabla, sin interpolar.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2326,22 +2326,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mod_length_wrong_rows</t>
+          <t>warp_undersized</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dimensiones de la Red</t>
+          <t>Cables de Remolque</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>G48</t>
+          <t>E267:E272</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Largo de la red modificada suma filas del plano inferior en vez de la bolsa.</t>
+          <t>Cable de 12 mm (8.55 t) seleccionado con carga mínima requerida de 8.8 t.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>footrope_mid_truncation</t>
+          <t>mod_length_wrong_rows</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>F46</t>
+          <t>G48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MID() sobre números trunca el burlón a 33.3 m (el valor completo es 33.389 m).</t>
+          <t>Largo de la red modificada suma filas del plano inferior en vez de la bolsa.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2390,22 +2390,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dpa_std_uses_mod_edy</t>
+          <t>footrope_mid_truncation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Dimensiones de la Red</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P164</t>
+          <t>F46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La DPA de Fridman de la red estándar usa el coeficiente Edy de la modificada.</t>
+          <t>MID() sobre números trunca el burlón a 33.3 m (el valor completo es 33.389 m).</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2422,86 +2422,86 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nomura_column_links_hamuro</t>
+          <t>dpa_std_uses_mod_edy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Potencia Disponible Arrastre OK</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>G319,G342,G362</t>
+          <t>P164</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>La columna 'Nomura' de los resúmenes enlaza a los resultados de Hamuro.</t>
+          <t>La DPA de Fridman de la red estándar usa el coeficiente Edy de la modificada.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>documentada</t>
+          <t>reproducida</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sin conmutador: Nomura se calcula de verdad; el enlace del libro sólo se documenta.</t>
+          <t>Reproducida (EXCEL).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sweep_degrees_of_sine</t>
+          <t>nomura_column_links_hamuro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portones y aparejamiento</t>
+          <t>Potencia Disponible Arrastre OK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>G71</t>
+          <t>G319,G342,G362</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DEGREES(SIN(20)) con el ángulo en grados y error de precedencia.</t>
+          <t>La columna 'Nomura' de los resúmenes enlaza a los resultados de Hamuro.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>documentada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reproducida (EXCEL).</t>
+          <t>Sin conmutador: Nomura se calcula de verdad; el enlace del libro sólo se documenta.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nomura_ratio_typo</t>
+          <t>sweep_degrees_of_sine</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tablas de Referencias</t>
+          <t>Portones y aparejamiento</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>G18,G21</t>
+          <t>G71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Proporción 10.6 donde el resto de la tabla sugiere 1.06.</t>
+          <t>DEGREES(SIN(20)) con el ángulo en grados y error de precedencia.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2511,110 +2511,110 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tabla de referencia copiada tal cual en ambos modos.</t>
+          <t>Reproducida (EXCEL).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>panel_f_cut_na</t>
+          <t>nomura_ratio_typo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paños de red y cortes</t>
+          <t>Tablas de Referencias</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T122</t>
+          <t>G18,G21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VLOOKUP/MATCH de la razón de corte del panel F devuelve #N/A.</t>
+          <t>Proporción 10.6 donde el resto de la tabla sugiere 1.06.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>corregida</t>
+          <t>reproducida</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El código de corte se calcula en ambos modos.</t>
+          <t>Tabla de referencia copiada tal cual en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>codend_minor_side_uses_depth</t>
+          <t>panel_f_cut_na</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Paños de red y cortes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K36:K37</t>
+          <t>T122</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lado menor de las bolsas I/J = Paños!H224 (N = 200) en vez de H223 (T2 = 113); infla Ss de 38.75 a 40.90 m² y St de 308.6 a 315.6 m².</t>
+          <t>VLOOKUP/MATCH de la razón de corte del panel F devuelve #N/A.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reproducida (EXCEL).</t>
+          <t>El código de corte se calcula en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>panel_b_cut_uses_plan_coef</t>
+          <t>codend_minor_side_uses_depth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paños de red y cortes</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>K36:K37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>La razón de corte del paño B usa P55 (coeficiente de plano 0.5) en vez de T56 (N).</t>
+          <t>Lado menor de las bolsas I/J = Paños!H224 (N = 200) en vez de H223 (T2 = 113); infla Ss de 38.75 a 40.90 m² y St de 308.6 a 315.6 m².</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>corregida</t>
+          <t>reproducida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La razón de corte usa N en ambos modos.</t>
+          <t>Reproducida (EXCEL).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>panel_b_cut_code_lookup_a</t>
+          <t>panel_b_cut_uses_plan_coef</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T62</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El código de corte del paño B se busca con la razón del paño A (H63).</t>
+          <t>La razón de corte del paño B usa P55 (coeficiente de plano 0.5) en vez de T56 (N).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2639,46 +2639,46 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cada paño busca con su propia razón.</t>
+          <t>La razón de corte usa N en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>net_weight_ignores_panel_count</t>
+          <t>panel_b_cut_code_lookup_a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Paños de red y cortes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>O107,O109</t>
+          <t>T62</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El peso total suma las filas sin multiplicar por la cantidad de paneles iguales.</t>
+          <t>El código de corte del paño B se busca con la razón del paño A (H63).</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Peso por fila del libro en ambos modos (documentado).</t>
+          <t>Cada paño busca con su propia razón.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>catenary_ratio_hardcoded</t>
+          <t>net_weight_ignores_panel_count</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>O266</t>
+          <t>O107,O109</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>fL/L = 0.216 fijo (corresponde a DPA/L = 0.87); el DPA/L del modelo (0.45) queda fuera de la tabla de catenaria.</t>
+          <t>El peso total suma las filas sin multiplicar por la cantidad de paneles iguales.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2703,29 +2703,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fL/L = 0.216 en ambos modos; el valor de tabla se anota en las notas.</t>
+          <t>Reproducida (EXCEL).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>float_lookup_unsorted</t>
+          <t>catenary_ratio_hardcoded</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Flotación y Lastre</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>F92</t>
+          <t>O266</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LOOKUP del diámetro de boya sobre el vector 'cincuenta' sin ordenar.</t>
+          <t>fL/L = 0.216 fijo (corresponde a DPA/L = 0.87); el DPA/L del modelo (0.45) queda fuera de la tabla de catenaria.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2735,44 +2735,76 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reproducida (EXCEL).</t>
+          <t>fL/L = 0.216 en ambos modos; el valor de tabla se anota en las notas.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>float_lookup_unsorted</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Flotación y Lastre</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>F92</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LOOKUP del diámetro de boya sobre el vector 'cincuenta' sin ordenar.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>reproducida</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Reproducida (EXCEL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>flotation_rounding_inconsistent</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Flotación y Lastre</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>M43:M50</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>ROUNDDOWN sólo en M42 y en el bloque de 180 HP; el resto de la columna sin redondear.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>reproducida</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Reproducida (EXCEL).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Celdas del libro: trawlkit.compat.ERRATA; docs/erratas.md</t>
         </is>
